--- a/databases/Attack Types.xlsx
+++ b/databases/Attack Types.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathr\Documents\MobileTesia\mobile-tesia\MobileTestia\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE5A8C7-040C-4360-879F-A7E7D6A176C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD53ED3-37AD-4014-8471-8B1B03C8E4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="189">
   <si>
     <t>Type</t>
   </si>
@@ -100,18 +100,519 @@
   </si>
   <si>
     <t>Self-buff (bandage) - applies contact_status_effect to player</t>
+  </si>
+  <si>
+    <t>Target Example</t>
+  </si>
+  <si>
+    <t>kill_named</t>
+  </si>
+  <si>
+    <t>Kill specific enemy</t>
+  </si>
+  <si>
+    <t>ene_vampire_lord</t>
+  </si>
+  <si>
+    <t>kill_count</t>
+  </si>
+  <si>
+    <t>Kill X of enemy type</t>
+  </si>
+  <si>
+    <t>ene_zombie_basic</t>
+  </si>
+  <si>
+    <t>gather</t>
+  </si>
+  <si>
+    <t>Collect X items</t>
+  </si>
+  <si>
+    <t>itm_wolf_pelt</t>
+  </si>
+  <si>
+    <t>talk</t>
+  </si>
+  <si>
+    <t>Talk to NPC</t>
+  </si>
+  <si>
+    <t>npc_village_elder</t>
+  </si>
+  <si>
+    <t>interact</t>
+  </si>
+  <si>
+    <t>Interact with object</t>
+  </si>
+  <si>
+    <t>chest_goblin</t>
+  </si>
+  <si>
+    <t>reach_location</t>
+  </si>
+  <si>
+    <t>Enter zone</t>
+  </si>
+  <si>
+    <t>zone_crypt</t>
+  </si>
+  <si>
+    <t>delivery</t>
+  </si>
+  <si>
+    <t>Bring item to NPC</t>
+  </si>
+  <si>
+    <t>npc_old_woman</t>
+  </si>
+  <si>
+    <t>Quests</t>
+  </si>
+  <si>
+    <t>Effects to be implemented</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Code Location</t>
+  </si>
+  <si>
+    <t>melee</t>
+  </si>
+  <si>
+    <t>Instant hitbox at target</t>
+  </si>
+  <si>
+    <t>✅ Implemented</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:179</t>
+  </si>
+  <si>
+    <t>aoe</t>
+  </si>
+  <si>
+    <t>Area damage around self</t>
+  </si>
+  <si>
+    <t>dash_attack</t>
+  </si>
+  <si>
+    <t>Rush to target, damage on arrival</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:181</t>
+  </si>
+  <si>
+    <t>projectile</t>
+  </si>
+  <si>
+    <t>Fire projectile toward target</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:183</t>
+  </si>
+  <si>
+    <t>teleport_attack</t>
+  </si>
+  <si>
+    <t>Teleport behind target and strike</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:185</t>
+  </si>
+  <si>
+    <t>pattern</t>
+  </si>
+  <si>
+    <t>Multi-directional attack</t>
+  </si>
+  <si>
+    <t>⚠️ Partial</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:187</t>
+  </si>
+  <si>
+    <t>beam</t>
+  </si>
+  <si>
+    <t>Sweeping line attack</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:189</t>
+  </si>
+  <si>
+    <t>circle</t>
+  </si>
+  <si>
+    <t>Radial area</t>
+  </si>
+  <si>
+    <t>hitbox_spawner.gd:101</t>
+  </si>
+  <si>
+    <t>cone</t>
+  </si>
+  <si>
+    <t>Arc/fan shape</t>
+  </si>
+  <si>
+    <t>hitbox_spawner.gd:124</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>Narrow rectangle</t>
+  </si>
+  <si>
+    <t>hitbox_spawner.gd:169</t>
+  </si>
+  <si>
+    <t>cross</t>
+  </si>
+  <si>
+    <t>4-directional pattern</t>
+  </si>
+  <si>
+    <t>hitbox_spawner.gd:197</t>
+  </si>
+  <si>
+    <t>ring</t>
+  </si>
+  <si>
+    <t>Expanding ring</t>
+  </si>
+  <si>
+    <t>hitbox_spawner.gd:229</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>physical</t>
+  </si>
+  <si>
+    <t>⚠️ Visual only</t>
+  </si>
+  <si>
+    <t>Colors hitbox, no resistance calc</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>Colors hitbox orange</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>Colors hitbox blue</t>
+  </si>
+  <si>
+    <t>lightning</t>
+  </si>
+  <si>
+    <t>Colors hitbox yellow</t>
+  </si>
+  <si>
+    <t>poison</t>
+  </si>
+  <si>
+    <t>Colors hitbox green</t>
+  </si>
+  <si>
+    <t>chaos</t>
+  </si>
+  <si>
+    <t>Colors hitbox purple</t>
+  </si>
+  <si>
+    <t>pure</t>
+  </si>
+  <si>
+    <t>Colors hitbox white</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>stun</t>
+  </si>
+  <si>
+    <t>stun:duration</t>
+  </si>
+  <si>
+    <t>⚠️ Calls method, not implemented on player</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:477</t>
+  </si>
+  <si>
+    <t>knockback</t>
+  </si>
+  <si>
+    <t>knockback:force</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:482</t>
+  </si>
+  <si>
+    <t>poison:duration:damage</t>
+  </si>
+  <si>
+    <t>⚠️ Calls method, not implemented</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:468</t>
+  </si>
+  <si>
+    <t>burn</t>
+  </si>
+  <si>
+    <t>burn:duration:damage</t>
+  </si>
+  <si>
+    <t>bleed</t>
+  </si>
+  <si>
+    <t>bleed:duration:damage</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:470</t>
+  </si>
+  <si>
+    <t>slow</t>
+  </si>
+  <si>
+    <t>slow:duration:percent</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:472</t>
+  </si>
+  <si>
+    <t>lifesteal</t>
+  </si>
+  <si>
+    <t>lifesteal:percent</t>
+  </si>
+  <si>
+    <t>ability_executor.gd:474</t>
+  </si>
+  <si>
+    <t>distance&gt;X</t>
+  </si>
+  <si>
+    <t>Distance check</t>
+  </si>
+  <si>
+    <t>ability_data.gd</t>
+  </si>
+  <si>
+    <t>distance&lt;X</t>
+  </si>
+  <si>
+    <t>health&lt;X%</t>
+  </si>
+  <si>
+    <t>Health percent check</t>
+  </si>
+  <si>
+    <t>health&gt;X%</t>
+  </si>
+  <si>
+    <t>stand</t>
+  </si>
+  <si>
+    <t>Stay in place</t>
+  </si>
+  <si>
+    <t>enemy_behavior.gd:109</t>
+  </si>
+  <si>
+    <t>roam</t>
+  </si>
+  <si>
+    <t>Wander randomly</t>
+  </si>
+  <si>
+    <t>❌ NOT Implemented</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>patrol</t>
+  </si>
+  <si>
+    <t>Follow patrol path</t>
+  </si>
+  <si>
+    <t>direct</t>
+  </si>
+  <si>
+    <t>Walk straight to target</t>
+  </si>
+  <si>
+    <t>✅ Implemented (default)</t>
+  </si>
+  <si>
+    <t>charge</t>
+  </si>
+  <si>
+    <t>Fast rush at target</t>
+  </si>
+  <si>
+    <t>kite</t>
+  </si>
+  <si>
+    <t>Maintain distance</t>
+  </si>
+  <si>
+    <t>phase</t>
+  </si>
+  <si>
+    <t>Teleport/blink approach</t>
+  </si>
+  <si>
+    <t>Strafe around target</t>
+  </si>
+  <si>
+    <t>highest</t>
+  </si>
+  <si>
+    <t>Use highest priority ability</t>
+  </si>
+  <si>
+    <t>enemy_ability_controller.gd:151</t>
+  </si>
+  <si>
+    <t>conditional</t>
+  </si>
+  <si>
+    <t>Prefer abilities with matching conditions</t>
+  </si>
+  <si>
+    <t>enemy_ability_controller.gd:153</t>
+  </si>
+  <si>
+    <t>random_weighted</t>
+  </si>
+  <si>
+    <t>Random weighted by priority</t>
+  </si>
+  <si>
+    <t>enemy_ability_controller.gd:155</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>flee_health_threshold</t>
+  </si>
+  <si>
+    <t>HP% to trigger flee</t>
+  </si>
+  <si>
+    <t>flee_speed_mult</t>
+  </si>
+  <si>
+    <t>Speed when fleeing</t>
+  </si>
+  <si>
+    <t>detection_range</t>
+  </si>
+  <si>
+    <t>✅ Applied</t>
+  </si>
+  <si>
+    <t>enemy_npc.gd:176</t>
+  </si>
+  <si>
+    <t>leash_range</t>
+  </si>
+  <si>
+    <t>enemy_npc.gd:181</t>
+  </si>
+  <si>
+    <t>preferred_range</t>
+  </si>
+  <si>
+    <t>enemy_npc.gd:186</t>
+  </si>
+  <si>
+    <t>chase_speed_mult</t>
+  </si>
+  <si>
+    <t>enemy_npc.gd:191</t>
+  </si>
+  <si>
+    <t>strafe_chance</t>
+  </si>
+  <si>
+    <t>Chance to sidestep</t>
+  </si>
+  <si>
+    <t>❌ NOT Used</t>
+  </si>
+  <si>
+    <t>kite_distance</t>
+  </si>
+  <si>
+    <t>Distance to maintain</t>
+  </si>
+  <si>
+    <t>kite_speed_mult</t>
+  </si>
+  <si>
+    <t>Kiting speed</t>
+  </si>
+  <si>
+    <t>circle_direction</t>
+  </si>
+  <si>
+    <t>Strafe direction</t>
+  </si>
+  <si>
+    <t>attack_retreat_distance</t>
+  </si>
+  <si>
+    <t>Backup after attack</t>
+  </si>
+  <si>
+    <t>attack_retreat_duration</t>
+  </si>
+  <si>
+    <t>Retreat time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DODGE, MISS, IMMUNE, ABSORB </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -135,8 +636,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -418,7 +920,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="List1"/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="36.26953125" customWidth="1"/>
@@ -567,6 +1069,918 @@
         <v>24</v>
       </c>
     </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>82</v>
+      </c>
+      <c r="B46" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>89</v>
+      </c>
+      <c r="B52" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>120</v>
+      </c>
+      <c r="B68" t="s">
+        <v>121</v>
+      </c>
+      <c r="C68" t="s">
+        <v>113</v>
+      </c>
+      <c r="D68" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" t="s">
+        <v>124</v>
+      </c>
+      <c r="C69" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>49</v>
+      </c>
+      <c r="B72" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" t="s">
+        <v>53</v>
+      </c>
+      <c r="D73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C74" t="s">
+        <v>53</v>
+      </c>
+      <c r="D74" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" t="s">
+        <v>131</v>
+      </c>
+      <c r="C75" t="s">
+        <v>53</v>
+      </c>
+      <c r="D75" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B76" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" t="s">
+        <v>53</v>
+      </c>
+      <c r="D76" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" t="s">
+        <v>134</v>
+      </c>
+      <c r="C81" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" t="s">
+        <v>137</v>
+      </c>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>140</v>
+      </c>
+      <c r="B83" t="s">
+        <v>141</v>
+      </c>
+      <c r="C83" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87" t="s">
+        <v>143</v>
+      </c>
+      <c r="C87" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>145</v>
+      </c>
+      <c r="B88" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" t="s">
+        <v>148</v>
+      </c>
+      <c r="C89" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>149</v>
+      </c>
+      <c r="B90" t="s">
+        <v>150</v>
+      </c>
+      <c r="C90" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>73</v>
+      </c>
+      <c r="B91" t="s">
+        <v>151</v>
+      </c>
+      <c r="C91" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>49</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>152</v>
+      </c>
+      <c r="B96" t="s">
+        <v>153</v>
+      </c>
+      <c r="C96" t="s">
+        <v>53</v>
+      </c>
+      <c r="D96" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" t="s">
+        <v>156</v>
+      </c>
+      <c r="C97" t="s">
+        <v>53</v>
+      </c>
+      <c r="D97" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>158</v>
+      </c>
+      <c r="B98" t="s">
+        <v>159</v>
+      </c>
+      <c r="C98" t="s">
+        <v>53</v>
+      </c>
+      <c r="D98" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>161</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" t="s">
+        <v>163</v>
+      </c>
+      <c r="C104" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>164</v>
+      </c>
+      <c r="B105" t="s">
+        <v>165</v>
+      </c>
+      <c r="C105" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>161</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>166</v>
+      </c>
+      <c r="B112" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>169</v>
+      </c>
+      <c r="B113" t="s">
+        <v>167</v>
+      </c>
+      <c r="C113" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>171</v>
+      </c>
+      <c r="B114" t="s">
+        <v>167</v>
+      </c>
+      <c r="C114" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>173</v>
+      </c>
+      <c r="B115" t="s">
+        <v>167</v>
+      </c>
+      <c r="C115" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>161</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>175</v>
+      </c>
+      <c r="B125" t="s">
+        <v>176</v>
+      </c>
+      <c r="C125" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>178</v>
+      </c>
+      <c r="B126" t="s">
+        <v>179</v>
+      </c>
+      <c r="C126" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>180</v>
+      </c>
+      <c r="B127" t="s">
+        <v>181</v>
+      </c>
+      <c r="C127" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>182</v>
+      </c>
+      <c r="B128" t="s">
+        <v>183</v>
+      </c>
+      <c r="C128" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>184</v>
+      </c>
+      <c r="B129" t="s">
+        <v>185</v>
+      </c>
+      <c r="C129" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>186</v>
+      </c>
+      <c r="B130" t="s">
+        <v>187</v>
+      </c>
+      <c r="C130" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
